--- a/output/yearly_population_iteration_99_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_99_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5174</v>
+        <v>6397</v>
       </c>
       <c r="C2" t="n">
-        <v>7691</v>
+        <v>8131</v>
       </c>
       <c r="D2" t="n">
-        <v>24814</v>
+        <v>31655</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3343</v>
+        <v>4125</v>
       </c>
       <c r="C3" t="n">
-        <v>6726</v>
+        <v>5056</v>
       </c>
       <c r="D3" t="n">
-        <v>13540</v>
+        <v>19010</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2730</v>
+        <v>3153</v>
       </c>
       <c r="C4" t="n">
-        <v>5246</v>
+        <v>3313</v>
       </c>
       <c r="D4" t="n">
-        <v>6923</v>
+        <v>8629</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1843</v>
+        <v>2044</v>
       </c>
       <c r="C5" t="n">
-        <v>4058</v>
+        <v>2641</v>
       </c>
       <c r="D5" t="n">
-        <v>2661</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1079</v>
+        <v>1226</v>
       </c>
       <c r="C6" t="n">
-        <v>2721</v>
+        <v>2168</v>
       </c>
       <c r="D6" t="n">
-        <v>1133</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="7">
@@ -850,10 +850,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>523</v>
+        <v>596</v>
       </c>
       <c r="C7" t="n">
-        <v>1678</v>
+        <v>1624</v>
       </c>
       <c r="D7" t="n">
         <v>643</v>
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="C8" t="n">
-        <v>803</v>
+        <v>905</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
-        <v>350</v>
+        <v>407</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6222</v>
+        <v>8621</v>
       </c>
       <c r="C2" t="n">
-        <v>8651</v>
+        <v>10482</v>
       </c>
       <c r="D2" t="n">
-        <v>28996</v>
+        <v>32808</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3390</v>
+        <v>4187</v>
       </c>
       <c r="C3" t="n">
-        <v>6301</v>
+        <v>5744</v>
       </c>
       <c r="D3" t="n">
-        <v>14163</v>
+        <v>19452</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2568</v>
+        <v>3061</v>
       </c>
       <c r="C4" t="n">
-        <v>5861</v>
+        <v>4048</v>
       </c>
       <c r="D4" t="n">
-        <v>7725</v>
+        <v>9978</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1975</v>
+        <v>2253</v>
       </c>
       <c r="C5" t="n">
-        <v>4493</v>
+        <v>2902</v>
       </c>
       <c r="D5" t="n">
-        <v>3275</v>
+        <v>3729</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1299</v>
+        <v>1438</v>
       </c>
       <c r="C6" t="n">
-        <v>3309</v>
+        <v>2338</v>
       </c>
       <c r="D6" t="n">
-        <v>1341</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>683</v>
+        <v>777</v>
       </c>
       <c r="C7" t="n">
-        <v>2131</v>
+        <v>1868</v>
       </c>
       <c r="D7" t="n">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>292</v>
+        <v>343</v>
       </c>
       <c r="C8" t="n">
-        <v>1188</v>
+        <v>1205</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="C9" t="n">
-        <v>537</v>
+        <v>616</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9393</v>
+        <v>9745</v>
       </c>
       <c r="C2" t="n">
-        <v>8607</v>
+        <v>8681</v>
       </c>
       <c r="D2" t="n">
-        <v>24244</v>
+        <v>28279</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3731</v>
+        <v>4865</v>
       </c>
       <c r="C3" t="n">
-        <v>6450</v>
+        <v>6835</v>
       </c>
       <c r="D3" t="n">
-        <v>15132</v>
+        <v>19885</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2475</v>
+        <v>3034</v>
       </c>
       <c r="C4" t="n">
-        <v>5877</v>
+        <v>4673</v>
       </c>
       <c r="D4" t="n">
-        <v>8479</v>
+        <v>11129</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1977</v>
+        <v>2297</v>
       </c>
       <c r="C5" t="n">
-        <v>4990</v>
+        <v>3336</v>
       </c>
       <c r="D5" t="n">
-        <v>3784</v>
+        <v>4479</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1437</v>
+        <v>1613</v>
       </c>
       <c r="C6" t="n">
-        <v>3735</v>
+        <v>2526</v>
       </c>
       <c r="D6" t="n">
-        <v>1601</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>836</v>
+        <v>938</v>
       </c>
       <c r="C7" t="n">
-        <v>2594</v>
+        <v>2042</v>
       </c>
       <c r="D7" t="n">
-        <v>784</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>398</v>
+        <v>459</v>
       </c>
       <c r="C8" t="n">
-        <v>1566</v>
+        <v>1470</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="C9" t="n">
-        <v>780</v>
+        <v>834</v>
       </c>
       <c r="D9" t="n">
         <v>332</v>
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>366</v>
+        <v>410</v>
       </c>
       <c r="D10" t="n">
         <v>255</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8319</v>
+        <v>8844</v>
       </c>
       <c r="C2" t="n">
-        <v>5783</v>
+        <v>5833</v>
       </c>
       <c r="D2" t="n">
-        <v>19976</v>
+        <v>23386</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4492</v>
+        <v>5693</v>
       </c>
       <c r="C3" t="n">
-        <v>9663</v>
+        <v>9556</v>
       </c>
       <c r="D3" t="n">
-        <v>16469</v>
+        <v>21638</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1826</v>
+        <v>2122</v>
       </c>
       <c r="C4" t="n">
-        <v>8062</v>
+        <v>5804</v>
       </c>
       <c r="D4" t="n">
-        <v>8195</v>
+        <v>10424</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1327</v>
+        <v>1490</v>
       </c>
       <c r="C5" t="n">
-        <v>3660</v>
+        <v>2475</v>
       </c>
       <c r="D5" t="n">
-        <v>2622</v>
+        <v>2905</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>866</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D6" t="n">
         <v>772</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2542</v>
-      </c>
-      <c r="D6" t="n">
-        <v>768</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="C7" t="n">
-        <v>1534</v>
+        <v>1440</v>
       </c>
       <c r="D7" t="n">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C8" t="n">
-        <v>764</v>
+        <v>817</v>
       </c>
       <c r="D8" t="n">
         <v>325</v>
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>358</v>
+        <v>401</v>
       </c>
       <c r="D9" t="n">
         <v>249</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4895</v>
+        <v>5234</v>
       </c>
       <c r="C2" t="n">
-        <v>3283</v>
+        <v>2909</v>
       </c>
       <c r="D2" t="n">
-        <v>13868</v>
+        <v>16204</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5216</v>
+        <v>6053</v>
       </c>
       <c r="C3" t="n">
-        <v>7136</v>
+        <v>7105</v>
       </c>
       <c r="D3" t="n">
-        <v>15997</v>
+        <v>20629</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2490</v>
+        <v>3053</v>
       </c>
       <c r="C4" t="n">
-        <v>8879</v>
+        <v>7671</v>
       </c>
       <c r="D4" t="n">
-        <v>9374</v>
+        <v>12029</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1458</v>
+        <v>1635</v>
       </c>
       <c r="C5" t="n">
-        <v>5618</v>
+        <v>3916</v>
       </c>
       <c r="D5" t="n">
-        <v>3288</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>922</v>
+        <v>1036</v>
       </c>
       <c r="C6" t="n">
-        <v>3093</v>
+        <v>2267</v>
       </c>
       <c r="D6" t="n">
-        <v>959</v>
+        <v>990</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="C7" t="n">
-        <v>1930</v>
+        <v>1720</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C8" t="n">
-        <v>1013</v>
+        <v>1036</v>
       </c>
       <c r="D8" t="n">
         <v>339</v>
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>413</v>
+        <v>457</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4720</v>
+        <v>6273</v>
       </c>
       <c r="C2" t="n">
-        <v>10969</v>
+        <v>9546</v>
       </c>
       <c r="D2" t="n">
-        <v>18659</v>
+        <v>15674</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4261</v>
+        <v>4791</v>
       </c>
       <c r="C3" t="n">
-        <v>4680</v>
+        <v>4507</v>
       </c>
       <c r="D3" t="n">
-        <v>14743</v>
+        <v>18770</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3160</v>
+        <v>3752</v>
       </c>
       <c r="C4" t="n">
-        <v>7824</v>
+        <v>7228</v>
       </c>
       <c r="D4" t="n">
-        <v>10079</v>
+        <v>12951</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1689</v>
+        <v>1981</v>
       </c>
       <c r="C5" t="n">
-        <v>7120</v>
+        <v>5674</v>
       </c>
       <c r="D5" t="n">
-        <v>4181</v>
+        <v>5035</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1055</v>
+        <v>1185</v>
       </c>
       <c r="C6" t="n">
-        <v>4201</v>
+        <v>2988</v>
       </c>
       <c r="D6" t="n">
-        <v>1303</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>507</v>
+        <v>577</v>
       </c>
       <c r="C7" t="n">
-        <v>2461</v>
+        <v>1977</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="C8" t="n">
-        <v>1399</v>
+        <v>1327</v>
       </c>
       <c r="D8" t="n">
         <v>358</v>
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>646</v>
+        <v>682</v>
       </c>
       <c r="D9" t="n">
         <v>264</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2807</v>
+        <v>3689</v>
       </c>
       <c r="C2" t="n">
-        <v>5040</v>
+        <v>4400</v>
       </c>
       <c r="D2" t="n">
-        <v>12866</v>
+        <v>10838</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4217</v>
+        <v>5015</v>
       </c>
       <c r="C3" t="n">
-        <v>6693</v>
+        <v>6096</v>
       </c>
       <c r="D3" t="n">
-        <v>14827</v>
+        <v>17972</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3512</v>
+        <v>4134</v>
       </c>
       <c r="C4" t="n">
-        <v>7431</v>
+        <v>6857</v>
       </c>
       <c r="D4" t="n">
-        <v>10841</v>
+        <v>13785</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1794</v>
+        <v>2066</v>
       </c>
       <c r="C5" t="n">
-        <v>8283</v>
+        <v>6862</v>
       </c>
       <c r="D5" t="n">
-        <v>4404</v>
+        <v>5434</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>897</v>
+        <v>1025</v>
       </c>
       <c r="C6" t="n">
-        <v>5093</v>
+        <v>3728</v>
       </c>
       <c r="D6" t="n">
-        <v>1278</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>2572</v>
+        <v>2201</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>1071</v>
+        <v>1084</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
         <v>165</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3520</v>
+        <v>4251</v>
       </c>
       <c r="C2" t="n">
-        <v>7213</v>
+        <v>8484</v>
       </c>
       <c r="D2" t="n">
-        <v>15866</v>
+        <v>13795</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3076</v>
+        <v>3803</v>
       </c>
       <c r="C3" t="n">
-        <v>5268</v>
+        <v>4721</v>
       </c>
       <c r="D3" t="n">
-        <v>13563</v>
+        <v>15794</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3352</v>
+        <v>3963</v>
       </c>
       <c r="C4" t="n">
-        <v>6993</v>
+        <v>6414</v>
       </c>
       <c r="D4" t="n">
-        <v>11161</v>
+        <v>14049</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2204</v>
+        <v>2566</v>
       </c>
       <c r="C5" t="n">
-        <v>7805</v>
+        <v>6782</v>
       </c>
       <c r="D5" t="n">
-        <v>5301</v>
+        <v>6603</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1135</v>
+        <v>1292</v>
       </c>
       <c r="C6" t="n">
-        <v>6443</v>
+        <v>5054</v>
       </c>
       <c r="D6" t="n">
-        <v>1681</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>339</v>
+        <v>397</v>
       </c>
       <c r="C7" t="n">
-        <v>3634</v>
+        <v>2835</v>
       </c>
       <c r="D7" t="n">
-        <v>669</v>
+        <v>685</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>1635</v>
+        <v>1531</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
         <v>173</v>
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2440</v>
+        <v>3192</v>
       </c>
       <c r="C2" t="n">
-        <v>3688</v>
+        <v>4681</v>
       </c>
       <c r="D2" t="n">
-        <v>12133</v>
+        <v>10205</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2820</v>
+        <v>3459</v>
       </c>
       <c r="C3" t="n">
-        <v>5529</v>
+        <v>5637</v>
       </c>
       <c r="D3" t="n">
-        <v>13101</v>
+        <v>14694</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2985</v>
+        <v>3604</v>
       </c>
       <c r="C4" t="n">
-        <v>6286</v>
+        <v>5766</v>
       </c>
       <c r="D4" t="n">
-        <v>11251</v>
+        <v>13991</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2428</v>
+        <v>2839</v>
       </c>
       <c r="C5" t="n">
-        <v>7646</v>
+        <v>6767</v>
       </c>
       <c r="D5" t="n">
-        <v>5916</v>
+        <v>7386</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1328</v>
+        <v>1515</v>
       </c>
       <c r="C6" t="n">
-        <v>7133</v>
+        <v>5798</v>
       </c>
       <c r="D6" t="n">
-        <v>2006</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>317</v>
+        <v>373</v>
       </c>
       <c r="C7" t="n">
-        <v>4570</v>
+        <v>3544</v>
       </c>
       <c r="D7" t="n">
-        <v>759</v>
+        <v>783</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>2113</v>
+        <v>1920</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>644</v>
+        <v>657</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>177</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4304</v>
+        <v>5015</v>
       </c>
       <c r="C2" t="n">
-        <v>4962</v>
+        <v>4777</v>
       </c>
       <c r="D2" t="n">
-        <v>12620</v>
+        <v>24016</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2259</v>
+        <v>2830</v>
       </c>
       <c r="C3" t="n">
-        <v>4300</v>
+        <v>4661</v>
       </c>
       <c r="D3" t="n">
-        <v>12146</v>
+        <v>13214</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2543</v>
+        <v>3087</v>
       </c>
       <c r="C4" t="n">
-        <v>5835</v>
+        <v>5590</v>
       </c>
       <c r="D4" t="n">
-        <v>11175</v>
+        <v>13666</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2412</v>
+        <v>2827</v>
       </c>
       <c r="C5" t="n">
-        <v>6938</v>
+        <v>6213</v>
       </c>
       <c r="D5" t="n">
-        <v>6453</v>
+        <v>7978</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1578</v>
+        <v>1833</v>
       </c>
       <c r="C6" t="n">
-        <v>7270</v>
+        <v>6129</v>
       </c>
       <c r="D6" t="n">
-        <v>2448</v>
+        <v>2966</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>563</v>
+        <v>661</v>
       </c>
       <c r="C7" t="n">
-        <v>5522</v>
+        <v>4438</v>
       </c>
       <c r="D7" t="n">
-        <v>910</v>
+        <v>970</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="C8" t="n">
-        <v>2999</v>
+        <v>2492</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1125</v>
+        <v>1084</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="D10" t="n">
         <v>185</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5976</v>
+        <v>8772</v>
       </c>
       <c r="C2" t="n">
-        <v>5891</v>
+        <v>9050</v>
       </c>
       <c r="D2" t="n">
-        <v>4800</v>
+        <v>5929</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3078</v>
+        <v>3589</v>
       </c>
       <c r="C2" t="n">
-        <v>2819</v>
+        <v>2713</v>
       </c>
       <c r="D2" t="n">
-        <v>9288</v>
+        <v>17676</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3126</v>
+        <v>3825</v>
       </c>
       <c r="C3" t="n">
-        <v>4825</v>
+        <v>5090</v>
       </c>
       <c r="D3" t="n">
-        <v>13218</v>
+        <v>15140</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3505</v>
+        <v>4190</v>
       </c>
       <c r="C4" t="n">
-        <v>8187</v>
+        <v>7767</v>
       </c>
       <c r="D4" t="n">
-        <v>11525</v>
+        <v>14039</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1524</v>
+        <v>1772</v>
       </c>
       <c r="C5" t="n">
-        <v>10228</v>
+        <v>8860</v>
       </c>
       <c r="D5" t="n">
-        <v>5845</v>
+        <v>7274</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>520</v>
+        <v>610</v>
       </c>
       <c r="C6" t="n">
-        <v>6836</v>
+        <v>5550</v>
       </c>
       <c r="D6" t="n">
-        <v>1975</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="C7" t="n">
-        <v>2939</v>
+        <v>2442</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1102</v>
+        <v>1062</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="D9" t="n">
         <v>181</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7105</v>
+        <v>7717</v>
       </c>
       <c r="C2" t="n">
-        <v>5158</v>
+        <v>4582</v>
       </c>
       <c r="D2" t="n">
-        <v>13496</v>
+        <v>16122</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2539</v>
+        <v>3724</v>
       </c>
       <c r="C3" t="n">
-        <v>3016</v>
+        <v>4561</v>
       </c>
       <c r="D3" t="n">
-        <v>1484</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5199</v>
+        <v>5117</v>
       </c>
       <c r="C2" t="n">
-        <v>7051</v>
+        <v>4389</v>
       </c>
       <c r="D2" t="n">
-        <v>25357</v>
+        <v>20517</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3958</v>
+        <v>4703</v>
       </c>
       <c r="C3" t="n">
-        <v>3658</v>
+        <v>3943</v>
       </c>
       <c r="D3" t="n">
-        <v>3392</v>
+        <v>3948</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1136</v>
+        <v>1652</v>
       </c>
       <c r="C4" t="n">
-        <v>1838</v>
+        <v>2716</v>
       </c>
       <c r="D4" t="n">
-        <v>1480</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5002</v>
+        <v>5196</v>
       </c>
       <c r="C2" t="n">
-        <v>5332</v>
+        <v>2573</v>
       </c>
       <c r="D2" t="n">
-        <v>26275</v>
+        <v>29756</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3757</v>
+        <v>4049</v>
       </c>
       <c r="C3" t="n">
-        <v>4767</v>
+        <v>3623</v>
       </c>
       <c r="D3" t="n">
-        <v>6662</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2155</v>
+        <v>2709</v>
       </c>
       <c r="C4" t="n">
-        <v>2830</v>
+        <v>3354</v>
       </c>
       <c r="D4" t="n">
-        <v>1802</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>526</v>
+        <v>723</v>
       </c>
       <c r="C5" t="n">
-        <v>1100</v>
+        <v>1580</v>
       </c>
       <c r="D5" t="n">
-        <v>1192</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5970</v>
+        <v>6736</v>
       </c>
       <c r="C2" t="n">
-        <v>5444</v>
+        <v>4057</v>
       </c>
       <c r="D2" t="n">
-        <v>25503</v>
+        <v>36910</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3577</v>
+        <v>3816</v>
       </c>
       <c r="C3" t="n">
-        <v>4402</v>
+        <v>2683</v>
       </c>
       <c r="D3" t="n">
-        <v>9174</v>
+        <v>9432</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2514</v>
+        <v>2856</v>
       </c>
       <c r="C4" t="n">
-        <v>3785</v>
+        <v>3428</v>
       </c>
       <c r="D4" t="n">
-        <v>2633</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1098</v>
+        <v>1412</v>
       </c>
       <c r="C5" t="n">
-        <v>1990</v>
+        <v>2466</v>
       </c>
       <c r="D5" t="n">
-        <v>1249</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>292</v>
+        <v>373</v>
       </c>
       <c r="C6" t="n">
-        <v>704</v>
+        <v>934</v>
       </c>
       <c r="D6" t="n">
         <v>946</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6080</v>
+        <v>6746</v>
       </c>
       <c r="C2" t="n">
-        <v>9267</v>
+        <v>4835</v>
       </c>
       <c r="D2" t="n">
-        <v>21722</v>
+        <v>34933</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3441</v>
+        <v>3798</v>
       </c>
       <c r="C3" t="n">
-        <v>4042</v>
+        <v>2773</v>
       </c>
       <c r="D3" t="n">
-        <v>10358</v>
+        <v>12177</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1878</v>
+        <v>2075</v>
       </c>
       <c r="C4" t="n">
-        <v>3350</v>
+        <v>2471</v>
       </c>
       <c r="D4" t="n">
-        <v>3248</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>940</v>
+        <v>1111</v>
       </c>
       <c r="C5" t="n">
-        <v>2149</v>
+        <v>2162</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>332</v>
+        <v>418</v>
       </c>
       <c r="C6" t="n">
-        <v>906</v>
+        <v>1133</v>
       </c>
       <c r="D6" t="n">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>337</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4951</v>
+        <v>6441</v>
       </c>
       <c r="C2" t="n">
-        <v>6835</v>
+        <v>4991</v>
       </c>
       <c r="D2" t="n">
-        <v>25375</v>
+        <v>40430</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3955</v>
+        <v>4381</v>
       </c>
       <c r="C3" t="n">
-        <v>6141</v>
+        <v>3421</v>
       </c>
       <c r="D3" t="n">
-        <v>11579</v>
+        <v>15103</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2321</v>
+        <v>2581</v>
       </c>
       <c r="C4" t="n">
-        <v>3705</v>
+        <v>2602</v>
       </c>
       <c r="D4" t="n">
-        <v>4650</v>
+        <v>4986</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1266</v>
+        <v>1425</v>
       </c>
       <c r="C5" t="n">
-        <v>2819</v>
+        <v>2277</v>
       </c>
       <c r="D5" t="n">
-        <v>1565</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>593</v>
+        <v>703</v>
       </c>
       <c r="C6" t="n">
-        <v>1610</v>
+        <v>1711</v>
       </c>
       <c r="D6" t="n">
-        <v>822</v>
+        <v>834</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="C7" t="n">
-        <v>660</v>
+        <v>819</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4503</v>
+        <v>5674</v>
       </c>
       <c r="C2" t="n">
-        <v>9753</v>
+        <v>7857</v>
       </c>
       <c r="D2" t="n">
-        <v>22824</v>
+        <v>32641</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3665</v>
+        <v>4428</v>
       </c>
       <c r="C3" t="n">
-        <v>5638</v>
+        <v>3702</v>
       </c>
       <c r="D3" t="n">
-        <v>12952</v>
+        <v>18067</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2713</v>
+        <v>2972</v>
       </c>
       <c r="C4" t="n">
-        <v>5031</v>
+        <v>3011</v>
       </c>
       <c r="D4" t="n">
-        <v>5794</v>
+        <v>6776</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1569</v>
+        <v>1766</v>
       </c>
       <c r="C5" t="n">
-        <v>3253</v>
+        <v>2407</v>
       </c>
       <c r="D5" t="n">
-        <v>2109</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>851</v>
+        <v>962</v>
       </c>
       <c r="C6" t="n">
-        <v>2241</v>
+        <v>1973</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>959</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>348</v>
+        <v>418</v>
       </c>
       <c r="C7" t="n">
-        <v>1162</v>
+        <v>1290</v>
       </c>
       <c r="D7" t="n">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="C8" t="n">
-        <v>473</v>
+        <v>575</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
         <v>155</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_99_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_99_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6397</v>
+        <v>7893</v>
       </c>
       <c r="C2" t="n">
-        <v>8131</v>
+        <v>9420</v>
       </c>
       <c r="D2" t="n">
-        <v>31655</v>
+        <v>32288</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4125</v>
+        <v>3869</v>
       </c>
       <c r="C3" t="n">
-        <v>5056</v>
+        <v>5381</v>
       </c>
       <c r="D3" t="n">
-        <v>19010</v>
+        <v>13682</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3153</v>
+        <v>3016</v>
       </c>
       <c r="C4" t="n">
-        <v>3313</v>
+        <v>4900</v>
       </c>
       <c r="D4" t="n">
-        <v>8629</v>
+        <v>6690</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2044</v>
+        <v>1890</v>
       </c>
       <c r="C5" t="n">
-        <v>2641</v>
+        <v>5027</v>
       </c>
       <c r="D5" t="n">
-        <v>2879</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1226</v>
+        <v>1103</v>
       </c>
       <c r="C6" t="n">
-        <v>2168</v>
+        <v>3483</v>
       </c>
       <c r="D6" t="n">
-        <v>1129</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>596</v>
+        <v>505</v>
       </c>
       <c r="C7" t="n">
-        <v>1624</v>
+        <v>1987</v>
       </c>
       <c r="D7" t="n">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>232</v>
+        <v>187</v>
       </c>
       <c r="C8" t="n">
-        <v>905</v>
+        <v>987</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1052,7 +1052,7 @@
         <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8621</v>
+        <v>7179</v>
       </c>
       <c r="C2" t="n">
-        <v>10482</v>
+        <v>8251</v>
       </c>
       <c r="D2" t="n">
-        <v>32808</v>
+        <v>35026</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4187</v>
+        <v>4533</v>
       </c>
       <c r="C3" t="n">
-        <v>5744</v>
+        <v>6327</v>
       </c>
       <c r="D3" t="n">
-        <v>19452</v>
+        <v>15292</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3061</v>
+        <v>2918</v>
       </c>
       <c r="C4" t="n">
-        <v>4048</v>
+        <v>5024</v>
       </c>
       <c r="D4" t="n">
-        <v>9978</v>
+        <v>7627</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2253</v>
+        <v>2084</v>
       </c>
       <c r="C5" t="n">
-        <v>2902</v>
+        <v>4816</v>
       </c>
       <c r="D5" t="n">
-        <v>3729</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1438</v>
+        <v>1305</v>
       </c>
       <c r="C6" t="n">
-        <v>2338</v>
+        <v>4097</v>
       </c>
       <c r="D6" t="n">
-        <v>1371</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>777</v>
+        <v>675</v>
       </c>
       <c r="C7" t="n">
-        <v>1868</v>
+        <v>2645</v>
       </c>
       <c r="D7" t="n">
-        <v>712</v>
+        <v>691</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>343</v>
+        <v>282</v>
       </c>
       <c r="C8" t="n">
-        <v>1205</v>
+        <v>1398</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="C9" t="n">
-        <v>616</v>
+        <v>659</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
         <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1363,7 +1363,7 @@
         <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9745</v>
+        <v>7843</v>
       </c>
       <c r="C2" t="n">
-        <v>8681</v>
+        <v>8212</v>
       </c>
       <c r="D2" t="n">
-        <v>28279</v>
+        <v>43974</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4865</v>
+        <v>4558</v>
       </c>
       <c r="C3" t="n">
-        <v>6835</v>
+        <v>6305</v>
       </c>
       <c r="D3" t="n">
-        <v>19885</v>
+        <v>16681</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3034</v>
+        <v>3020</v>
       </c>
       <c r="C4" t="n">
-        <v>4673</v>
+        <v>5421</v>
       </c>
       <c r="D4" t="n">
-        <v>11129</v>
+        <v>8425</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2297</v>
+        <v>2146</v>
       </c>
       <c r="C5" t="n">
-        <v>3336</v>
+        <v>4755</v>
       </c>
       <c r="D5" t="n">
-        <v>4479</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1613</v>
+        <v>1481</v>
       </c>
       <c r="C6" t="n">
-        <v>2526</v>
+        <v>4350</v>
       </c>
       <c r="D6" t="n">
-        <v>1692</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>938</v>
+        <v>822</v>
       </c>
       <c r="C7" t="n">
-        <v>2042</v>
+        <v>3187</v>
       </c>
       <c r="D7" t="n">
-        <v>788</v>
+        <v>763</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>459</v>
+        <v>379</v>
       </c>
       <c r="C8" t="n">
-        <v>1470</v>
+        <v>1860</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="C9" t="n">
-        <v>834</v>
+        <v>933</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
         <v>225</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1674,7 +1674,7 @@
         <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8844</v>
+        <v>7293</v>
       </c>
       <c r="C2" t="n">
-        <v>5833</v>
+        <v>5649</v>
       </c>
       <c r="D2" t="n">
-        <v>23386</v>
+        <v>35979</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5693</v>
+        <v>5446</v>
       </c>
       <c r="C3" t="n">
-        <v>9556</v>
+        <v>9262</v>
       </c>
       <c r="D3" t="n">
-        <v>21638</v>
+        <v>17801</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2122</v>
+        <v>1982</v>
       </c>
       <c r="C4" t="n">
-        <v>5804</v>
+        <v>7479</v>
       </c>
       <c r="D4" t="n">
-        <v>10424</v>
+        <v>7993</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1490</v>
+        <v>1368</v>
       </c>
       <c r="C5" t="n">
-        <v>2475</v>
+        <v>4263</v>
       </c>
       <c r="D5" t="n">
-        <v>2905</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>866</v>
+        <v>759</v>
       </c>
       <c r="C6" t="n">
-        <v>2001</v>
+        <v>3123</v>
       </c>
       <c r="D6" t="n">
-        <v>772</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>424</v>
+        <v>350</v>
       </c>
       <c r="C7" t="n">
-        <v>1440</v>
+        <v>1822</v>
       </c>
       <c r="D7" t="n">
-        <v>472</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="C8" t="n">
-        <v>817</v>
+        <v>914</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
         <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1971,7 +1971,7 @@
         <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5234</v>
+        <v>4434</v>
       </c>
       <c r="C2" t="n">
-        <v>2909</v>
+        <v>3132</v>
       </c>
       <c r="D2" t="n">
-        <v>16204</v>
+        <v>25669</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6053</v>
+        <v>5396</v>
       </c>
       <c r="C3" t="n">
-        <v>7105</v>
+        <v>6928</v>
       </c>
       <c r="D3" t="n">
-        <v>20629</v>
+        <v>19418</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3053</v>
+        <v>2860</v>
       </c>
       <c r="C4" t="n">
-        <v>7671</v>
+        <v>8432</v>
       </c>
       <c r="D4" t="n">
-        <v>12029</v>
+        <v>9239</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1635</v>
+        <v>1504</v>
       </c>
       <c r="C5" t="n">
-        <v>3916</v>
+        <v>5675</v>
       </c>
       <c r="D5" t="n">
-        <v>3810</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1036</v>
+        <v>904</v>
       </c>
       <c r="C6" t="n">
-        <v>2267</v>
+        <v>3666</v>
       </c>
       <c r="D6" t="n">
-        <v>990</v>
+        <v>927</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>398</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>1720</v>
+        <v>2326</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>1036</v>
+        <v>1187</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
         <v>210</v>
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2268,7 +2268,7 @@
         <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6273</v>
+        <v>4031</v>
       </c>
       <c r="C2" t="n">
-        <v>9546</v>
+        <v>4518</v>
       </c>
       <c r="D2" t="n">
-        <v>15674</v>
+        <v>24213</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4791</v>
+        <v>4202</v>
       </c>
       <c r="C3" t="n">
-        <v>4507</v>
+        <v>4603</v>
       </c>
       <c r="D3" t="n">
-        <v>18770</v>
+        <v>18963</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3752</v>
+        <v>3395</v>
       </c>
       <c r="C4" t="n">
-        <v>7228</v>
+        <v>7534</v>
       </c>
       <c r="D4" t="n">
-        <v>12951</v>
+        <v>10619</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1981</v>
+        <v>1829</v>
       </c>
       <c r="C5" t="n">
-        <v>5674</v>
+        <v>6827</v>
       </c>
       <c r="D5" t="n">
-        <v>5035</v>
+        <v>3940</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1185</v>
+        <v>1054</v>
       </c>
       <c r="C6" t="n">
-        <v>2988</v>
+        <v>4553</v>
       </c>
       <c r="D6" t="n">
-        <v>1409</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>577</v>
+        <v>484</v>
       </c>
       <c r="C7" t="n">
-        <v>1977</v>
+        <v>2889</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="C8" t="n">
-        <v>1327</v>
+        <v>1655</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>682</v>
+        <v>742</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3689</v>
+        <v>2447</v>
       </c>
       <c r="C2" t="n">
-        <v>4400</v>
+        <v>2171</v>
       </c>
       <c r="D2" t="n">
-        <v>10838</v>
+        <v>16899</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5015</v>
+        <v>4017</v>
       </c>
       <c r="C3" t="n">
-        <v>6096</v>
+        <v>4442</v>
       </c>
       <c r="D3" t="n">
-        <v>17972</v>
+        <v>19084</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4134</v>
+        <v>3712</v>
       </c>
       <c r="C4" t="n">
-        <v>6857</v>
+        <v>7172</v>
       </c>
       <c r="D4" t="n">
-        <v>13785</v>
+        <v>11564</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2066</v>
+        <v>1890</v>
       </c>
       <c r="C5" t="n">
-        <v>6862</v>
+        <v>8012</v>
       </c>
       <c r="D5" t="n">
-        <v>5434</v>
+        <v>4182</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1025</v>
+        <v>865</v>
       </c>
       <c r="C6" t="n">
-        <v>3728</v>
+        <v>5456</v>
       </c>
       <c r="D6" t="n">
-        <v>1366</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="C7" t="n">
-        <v>2201</v>
+        <v>3016</v>
       </c>
       <c r="D7" t="n">
-        <v>586</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1084</v>
+        <v>1229</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4251</v>
+        <v>3932</v>
       </c>
       <c r="C2" t="n">
-        <v>8484</v>
+        <v>7028</v>
       </c>
       <c r="D2" t="n">
-        <v>13795</v>
+        <v>13997</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3803</v>
+        <v>2890</v>
       </c>
       <c r="C3" t="n">
-        <v>4721</v>
+        <v>3043</v>
       </c>
       <c r="D3" t="n">
-        <v>15794</v>
+        <v>17687</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3963</v>
+        <v>3390</v>
       </c>
       <c r="C4" t="n">
-        <v>6414</v>
+        <v>5807</v>
       </c>
       <c r="D4" t="n">
-        <v>14049</v>
+        <v>12367</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2566</v>
+        <v>2311</v>
       </c>
       <c r="C5" t="n">
-        <v>6782</v>
+        <v>7551</v>
       </c>
       <c r="D5" t="n">
-        <v>6603</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1292</v>
+        <v>1124</v>
       </c>
       <c r="C6" t="n">
-        <v>5054</v>
+        <v>6515</v>
       </c>
       <c r="D6" t="n">
-        <v>1894</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>397</v>
+        <v>324</v>
       </c>
       <c r="C7" t="n">
-        <v>2835</v>
+        <v>4030</v>
       </c>
       <c r="D7" t="n">
-        <v>685</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>1531</v>
+        <v>1883</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>570</v>
+        <v>604</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3131,7 +3131,7 @@
         <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3192</v>
+        <v>2712</v>
       </c>
       <c r="C2" t="n">
-        <v>4681</v>
+        <v>4821</v>
       </c>
       <c r="D2" t="n">
-        <v>10205</v>
+        <v>10204</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3459</v>
+        <v>2824</v>
       </c>
       <c r="C3" t="n">
-        <v>5637</v>
+        <v>4168</v>
       </c>
       <c r="D3" t="n">
-        <v>14694</v>
+        <v>16451</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3604</v>
+        <v>2991</v>
       </c>
       <c r="C4" t="n">
-        <v>5766</v>
+        <v>4739</v>
       </c>
       <c r="D4" t="n">
-        <v>13991</v>
+        <v>12773</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2839</v>
+        <v>2514</v>
       </c>
       <c r="C5" t="n">
-        <v>6767</v>
+        <v>7064</v>
       </c>
       <c r="D5" t="n">
-        <v>7386</v>
+        <v>5776</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1515</v>
+        <v>1318</v>
       </c>
       <c r="C6" t="n">
-        <v>5798</v>
+        <v>7099</v>
       </c>
       <c r="D6" t="n">
-        <v>2315</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>373</v>
+        <v>292</v>
       </c>
       <c r="C7" t="n">
-        <v>3544</v>
+        <v>4889</v>
       </c>
       <c r="D7" t="n">
-        <v>783</v>
+        <v>711</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>1920</v>
+        <v>2393</v>
       </c>
       <c r="D8" t="n">
-        <v>416</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>657</v>
+        <v>684</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5015</v>
+        <v>5041</v>
       </c>
       <c r="C2" t="n">
-        <v>4777</v>
+        <v>5552</v>
       </c>
       <c r="D2" t="n">
-        <v>24016</v>
+        <v>12695</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2830</v>
+        <v>2344</v>
       </c>
       <c r="C3" t="n">
-        <v>4661</v>
+        <v>3937</v>
       </c>
       <c r="D3" t="n">
-        <v>13214</v>
+        <v>14648</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3087</v>
+        <v>2549</v>
       </c>
       <c r="C4" t="n">
-        <v>5590</v>
+        <v>4399</v>
       </c>
       <c r="D4" t="n">
-        <v>13666</v>
+        <v>12914</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2827</v>
+        <v>2443</v>
       </c>
       <c r="C5" t="n">
-        <v>6213</v>
+        <v>5979</v>
       </c>
       <c r="D5" t="n">
-        <v>7978</v>
+        <v>6540</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1833</v>
+        <v>1596</v>
       </c>
       <c r="C6" t="n">
-        <v>6129</v>
+        <v>7025</v>
       </c>
       <c r="D6" t="n">
-        <v>2966</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>661</v>
+        <v>543</v>
       </c>
       <c r="C7" t="n">
-        <v>4438</v>
+        <v>5757</v>
       </c>
       <c r="D7" t="n">
-        <v>970</v>
+        <v>846</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>2492</v>
+        <v>3248</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1084</v>
+        <v>1243</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -3697,7 +3697,7 @@
         <v>364</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
         <v>94</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8772</v>
+        <v>6104</v>
       </c>
       <c r="C2" t="n">
-        <v>9050</v>
+        <v>10578</v>
       </c>
       <c r="D2" t="n">
-        <v>5929</v>
+        <v>5774</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3589</v>
+        <v>3642</v>
       </c>
       <c r="C2" t="n">
-        <v>2713</v>
+        <v>3198</v>
       </c>
       <c r="D2" t="n">
-        <v>17676</v>
+        <v>9343</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3825</v>
+        <v>3225</v>
       </c>
       <c r="C3" t="n">
-        <v>5090</v>
+        <v>4645</v>
       </c>
       <c r="D3" t="n">
-        <v>15140</v>
+        <v>15742</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4190</v>
+        <v>3558</v>
       </c>
       <c r="C4" t="n">
-        <v>7767</v>
+        <v>6495</v>
       </c>
       <c r="D4" t="n">
-        <v>14039</v>
+        <v>13099</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1772</v>
+        <v>1519</v>
       </c>
       <c r="C5" t="n">
-        <v>8860</v>
+        <v>9353</v>
       </c>
       <c r="D5" t="n">
-        <v>7274</v>
+        <v>5873</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>610</v>
+        <v>501</v>
       </c>
       <c r="C6" t="n">
-        <v>5550</v>
+        <v>7018</v>
       </c>
       <c r="D6" t="n">
-        <v>2280</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>2442</v>
+        <v>3183</v>
       </c>
       <c r="D7" t="n">
-        <v>568</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1062</v>
+        <v>1218</v>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -4305,7 +4305,7 @@
         <v>356</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
         <v>92</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7717</v>
+        <v>7301</v>
       </c>
       <c r="C2" t="n">
-        <v>4582</v>
+        <v>4937</v>
       </c>
       <c r="D2" t="n">
-        <v>16122</v>
+        <v>12385</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3724</v>
+        <v>2593</v>
       </c>
       <c r="C3" t="n">
-        <v>4561</v>
+        <v>5331</v>
       </c>
       <c r="D3" t="n">
-        <v>1635</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="4">
@@ -4554,7 +4554,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
         <v>381</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5117</v>
+        <v>5233</v>
       </c>
       <c r="C2" t="n">
-        <v>4389</v>
+        <v>4412</v>
       </c>
       <c r="D2" t="n">
-        <v>20517</v>
+        <v>19180</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4703</v>
+        <v>4061</v>
       </c>
       <c r="C3" t="n">
-        <v>3943</v>
+        <v>4405</v>
       </c>
       <c r="D3" t="n">
-        <v>3948</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1652</v>
+        <v>1161</v>
       </c>
       <c r="C4" t="n">
-        <v>2716</v>
+        <v>3167</v>
       </c>
       <c r="D4" t="n">
-        <v>1510</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="5">
@@ -4865,7 +4865,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
         <v>219</v>
@@ -4885,7 +4885,7 @@
         <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5196</v>
+        <v>5647</v>
       </c>
       <c r="C2" t="n">
-        <v>2573</v>
+        <v>9428</v>
       </c>
       <c r="D2" t="n">
-        <v>29756</v>
+        <v>25419</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4049</v>
+        <v>3815</v>
       </c>
       <c r="C3" t="n">
-        <v>3623</v>
+        <v>3816</v>
       </c>
       <c r="D3" t="n">
-        <v>6314</v>
+        <v>5603</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2709</v>
+        <v>2219</v>
       </c>
       <c r="C4" t="n">
-        <v>3354</v>
+        <v>3802</v>
       </c>
       <c r="D4" t="n">
-        <v>1932</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="5">
@@ -5176,10 +5176,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>723</v>
+        <v>526</v>
       </c>
       <c r="C5" t="n">
-        <v>1580</v>
+        <v>1827</v>
       </c>
       <c r="D5" t="n">
         <v>1206</v>
@@ -5196,7 +5196,7 @@
         <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6736</v>
+        <v>6064</v>
       </c>
       <c r="C2" t="n">
-        <v>4057</v>
+        <v>11573</v>
       </c>
       <c r="D2" t="n">
-        <v>36910</v>
+        <v>26914</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3816</v>
+        <v>3878</v>
       </c>
       <c r="C3" t="n">
-        <v>2683</v>
+        <v>5835</v>
       </c>
       <c r="D3" t="n">
-        <v>9432</v>
+        <v>8220</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2856</v>
+        <v>2534</v>
       </c>
       <c r="C4" t="n">
-        <v>3428</v>
+        <v>3730</v>
       </c>
       <c r="D4" t="n">
-        <v>2672</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1412</v>
+        <v>1122</v>
       </c>
       <c r="C5" t="n">
-        <v>2466</v>
+        <v>2812</v>
       </c>
       <c r="D5" t="n">
-        <v>1283</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>373</v>
+        <v>293</v>
       </c>
       <c r="C6" t="n">
-        <v>934</v>
+        <v>1058</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>942</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -5535,7 +5535,7 @@
         <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
         <v>189</v>
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6746</v>
+        <v>6334</v>
       </c>
       <c r="C2" t="n">
-        <v>4835</v>
+        <v>6378</v>
       </c>
       <c r="D2" t="n">
-        <v>34933</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3798</v>
+        <v>3590</v>
       </c>
       <c r="C3" t="n">
-        <v>2773</v>
+        <v>7231</v>
       </c>
       <c r="D3" t="n">
-        <v>12177</v>
+        <v>9861</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2075</v>
+        <v>1990</v>
       </c>
       <c r="C4" t="n">
-        <v>2471</v>
+        <v>3956</v>
       </c>
       <c r="D4" t="n">
-        <v>3338</v>
+        <v>2986</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1111</v>
+        <v>944</v>
       </c>
       <c r="C5" t="n">
-        <v>2162</v>
+        <v>2397</v>
       </c>
       <c r="D5" t="n">
-        <v>1192</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>418</v>
+        <v>331</v>
       </c>
       <c r="C6" t="n">
-        <v>1133</v>
+        <v>1289</v>
       </c>
       <c r="D6" t="n">
-        <v>763</v>
+        <v>758</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
         <v>235</v>
@@ -5888,7 +5888,7 @@
         <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6441</v>
+        <v>6483</v>
       </c>
       <c r="C2" t="n">
-        <v>4991</v>
+        <v>4446</v>
       </c>
       <c r="D2" t="n">
-        <v>40430</v>
+        <v>27115</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4381</v>
+        <v>4103</v>
       </c>
       <c r="C3" t="n">
-        <v>3421</v>
+        <v>5782</v>
       </c>
       <c r="D3" t="n">
-        <v>15103</v>
+        <v>11762</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2581</v>
+        <v>2421</v>
       </c>
       <c r="C4" t="n">
-        <v>2602</v>
+        <v>5854</v>
       </c>
       <c r="D4" t="n">
-        <v>4986</v>
+        <v>4252</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1425</v>
+        <v>1309</v>
       </c>
       <c r="C5" t="n">
-        <v>2277</v>
+        <v>3260</v>
       </c>
       <c r="D5" t="n">
-        <v>1588</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>703</v>
+        <v>586</v>
       </c>
       <c r="C6" t="n">
-        <v>1711</v>
+        <v>1900</v>
       </c>
       <c r="D6" t="n">
-        <v>834</v>
+        <v>821</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>240</v>
+        <v>194</v>
       </c>
       <c r="C7" t="n">
-        <v>819</v>
+        <v>916</v>
       </c>
       <c r="D7" t="n">
         <v>549</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
         <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
         <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6266,7 +6266,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5674</v>
+        <v>5075</v>
       </c>
       <c r="C2" t="n">
-        <v>7857</v>
+        <v>7966</v>
       </c>
       <c r="D2" t="n">
-        <v>32641</v>
+        <v>21921</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4428</v>
+        <v>4359</v>
       </c>
       <c r="C3" t="n">
-        <v>3702</v>
+        <v>4394</v>
       </c>
       <c r="D3" t="n">
-        <v>18067</v>
+        <v>13371</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2972</v>
+        <v>2771</v>
       </c>
       <c r="C4" t="n">
-        <v>3011</v>
+        <v>5692</v>
       </c>
       <c r="D4" t="n">
-        <v>6776</v>
+        <v>5564</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1766</v>
+        <v>1634</v>
       </c>
       <c r="C5" t="n">
-        <v>2407</v>
+        <v>4555</v>
       </c>
       <c r="D5" t="n">
-        <v>2144</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>962</v>
+        <v>847</v>
       </c>
       <c r="C6" t="n">
-        <v>1973</v>
+        <v>2596</v>
       </c>
       <c r="D6" t="n">
-        <v>959</v>
+        <v>929</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>418</v>
+        <v>342</v>
       </c>
       <c r="C7" t="n">
-        <v>1290</v>
+        <v>1426</v>
       </c>
       <c r="D7" t="n">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>575</v>
+        <v>624</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
         <v>202</v>
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6650,7 +6650,7 @@
         <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_99_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_99_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7893</v>
+        <v>1042</v>
       </c>
       <c r="C2" t="n">
-        <v>9420</v>
+        <v>2466</v>
       </c>
       <c r="D2" t="n">
-        <v>32288</v>
+        <v>13742</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3869</v>
+        <v>1937</v>
       </c>
       <c r="C3" t="n">
-        <v>5381</v>
+        <v>7477</v>
       </c>
       <c r="D3" t="n">
-        <v>13682</v>
+        <v>11997</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3016</v>
+        <v>1380</v>
       </c>
       <c r="C4" t="n">
-        <v>4900</v>
+        <v>11049</v>
       </c>
       <c r="D4" t="n">
-        <v>6690</v>
+        <v>4571</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1890</v>
+        <v>688</v>
       </c>
       <c r="C5" t="n">
-        <v>5027</v>
+        <v>7421</v>
       </c>
       <c r="D5" t="n">
-        <v>2496</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1103</v>
+        <v>270</v>
       </c>
       <c r="C6" t="n">
-        <v>3483</v>
+        <v>3266</v>
       </c>
       <c r="D6" t="n">
-        <v>1070</v>
+        <v>709</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>505</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>1987</v>
+        <v>1086</v>
       </c>
       <c r="D7" t="n">
-        <v>641</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>187</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>987</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>431</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7179</v>
+        <v>799</v>
       </c>
       <c r="C2" t="n">
-        <v>8251</v>
+        <v>5415</v>
       </c>
       <c r="D2" t="n">
-        <v>35026</v>
+        <v>14888</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4533</v>
+        <v>1299</v>
       </c>
       <c r="C3" t="n">
-        <v>6327</v>
+        <v>4386</v>
       </c>
       <c r="D3" t="n">
-        <v>15292</v>
+        <v>11532</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2918</v>
+        <v>1419</v>
       </c>
       <c r="C4" t="n">
-        <v>5024</v>
+        <v>8967</v>
       </c>
       <c r="D4" t="n">
-        <v>7627</v>
+        <v>5715</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2084</v>
+        <v>876</v>
       </c>
       <c r="C5" t="n">
-        <v>4816</v>
+        <v>9148</v>
       </c>
       <c r="D5" t="n">
-        <v>3040</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1305</v>
+        <v>406</v>
       </c>
       <c r="C6" t="n">
-        <v>4097</v>
+        <v>5219</v>
       </c>
       <c r="D6" t="n">
-        <v>1274</v>
+        <v>833</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>675</v>
+        <v>146</v>
       </c>
       <c r="C7" t="n">
-        <v>2645</v>
+        <v>2078</v>
       </c>
       <c r="D7" t="n">
-        <v>691</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1398</v>
+        <v>680</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>659</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>304</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7843</v>
+        <v>440</v>
       </c>
       <c r="C2" t="n">
-        <v>8212</v>
+        <v>2455</v>
       </c>
       <c r="D2" t="n">
-        <v>43974</v>
+        <v>10278</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4558</v>
+        <v>1134</v>
       </c>
       <c r="C3" t="n">
-        <v>6305</v>
+        <v>4602</v>
       </c>
       <c r="D3" t="n">
-        <v>16681</v>
+        <v>11631</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3020</v>
+        <v>1531</v>
       </c>
       <c r="C4" t="n">
-        <v>5421</v>
+        <v>8014</v>
       </c>
       <c r="D4" t="n">
-        <v>8425</v>
+        <v>6374</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2146</v>
+        <v>866</v>
       </c>
       <c r="C5" t="n">
-        <v>4755</v>
+        <v>10385</v>
       </c>
       <c r="D5" t="n">
-        <v>3608</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1481</v>
+        <v>307</v>
       </c>
       <c r="C6" t="n">
-        <v>4350</v>
+        <v>6274</v>
       </c>
       <c r="D6" t="n">
-        <v>1482</v>
+        <v>855</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>822</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>3187</v>
+        <v>1871</v>
       </c>
       <c r="D7" t="n">
-        <v>763</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>379</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1860</v>
+        <v>530</v>
       </c>
       <c r="D8" t="n">
-        <v>475</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>146</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>933</v>
+        <v>229</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>426</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>225</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7293</v>
+        <v>616</v>
       </c>
       <c r="C2" t="n">
-        <v>5649</v>
+        <v>13503</v>
       </c>
       <c r="D2" t="n">
-        <v>35979</v>
+        <v>11271</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5446</v>
+        <v>721</v>
       </c>
       <c r="C3" t="n">
-        <v>9262</v>
+        <v>3161</v>
       </c>
       <c r="D3" t="n">
-        <v>17801</v>
+        <v>10747</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1982</v>
+        <v>1204</v>
       </c>
       <c r="C4" t="n">
-        <v>7479</v>
+        <v>6220</v>
       </c>
       <c r="D4" t="n">
-        <v>7993</v>
+        <v>7038</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1368</v>
+        <v>1023</v>
       </c>
       <c r="C5" t="n">
-        <v>4263</v>
+        <v>9153</v>
       </c>
       <c r="D5" t="n">
-        <v>2422</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>759</v>
+        <v>473</v>
       </c>
       <c r="C6" t="n">
-        <v>3123</v>
+        <v>8090</v>
       </c>
       <c r="D6" t="n">
-        <v>747</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>350</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>1822</v>
+        <v>3762</v>
       </c>
       <c r="D7" t="n">
-        <v>465</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>914</v>
+        <v>1057</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>417</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4434</v>
+        <v>366</v>
       </c>
       <c r="C2" t="n">
-        <v>3132</v>
+        <v>6988</v>
       </c>
       <c r="D2" t="n">
-        <v>25669</v>
+        <v>8606</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5396</v>
+        <v>600</v>
       </c>
       <c r="C3" t="n">
-        <v>6928</v>
+        <v>6746</v>
       </c>
       <c r="D3" t="n">
-        <v>19418</v>
+        <v>10212</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2860</v>
+        <v>965</v>
       </c>
       <c r="C4" t="n">
-        <v>8432</v>
+        <v>4948</v>
       </c>
       <c r="D4" t="n">
-        <v>9239</v>
+        <v>7493</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1504</v>
+        <v>1059</v>
       </c>
       <c r="C5" t="n">
-        <v>5675</v>
+        <v>8187</v>
       </c>
       <c r="D5" t="n">
-        <v>3090</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>904</v>
+        <v>577</v>
       </c>
       <c r="C6" t="n">
-        <v>3666</v>
+        <v>8775</v>
       </c>
       <c r="D6" t="n">
-        <v>927</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>2326</v>
+        <v>5163</v>
       </c>
       <c r="D7" t="n">
-        <v>504</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1187</v>
+        <v>1647</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>465</v>
+        <v>420</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4031</v>
+        <v>367</v>
       </c>
       <c r="C2" t="n">
-        <v>4518</v>
+        <v>8685</v>
       </c>
       <c r="D2" t="n">
-        <v>24213</v>
+        <v>13185</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4202</v>
+        <v>431</v>
       </c>
       <c r="C3" t="n">
-        <v>4603</v>
+        <v>6059</v>
       </c>
       <c r="D3" t="n">
-        <v>18963</v>
+        <v>9336</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3395</v>
+        <v>720</v>
       </c>
       <c r="C4" t="n">
-        <v>7534</v>
+        <v>5656</v>
       </c>
       <c r="D4" t="n">
-        <v>10619</v>
+        <v>7682</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1829</v>
+        <v>951</v>
       </c>
       <c r="C5" t="n">
-        <v>6827</v>
+        <v>6696</v>
       </c>
       <c r="D5" t="n">
-        <v>3940</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1054</v>
+        <v>696</v>
       </c>
       <c r="C6" t="n">
-        <v>4553</v>
+        <v>8460</v>
       </c>
       <c r="D6" t="n">
-        <v>1226</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>484</v>
+        <v>251</v>
       </c>
       <c r="C7" t="n">
-        <v>2889</v>
+        <v>6576</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>162</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>1655</v>
+        <v>2971</v>
       </c>
       <c r="D8" t="n">
-        <v>350</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>742</v>
+        <v>844</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2447</v>
+        <v>255</v>
       </c>
       <c r="C2" t="n">
-        <v>2171</v>
+        <v>4795</v>
       </c>
       <c r="D2" t="n">
-        <v>16899</v>
+        <v>9705</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4017</v>
+        <v>626</v>
       </c>
       <c r="C3" t="n">
-        <v>4442</v>
+        <v>7214</v>
       </c>
       <c r="D3" t="n">
-        <v>19084</v>
+        <v>10248</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3712</v>
+        <v>1236</v>
       </c>
       <c r="C4" t="n">
-        <v>7172</v>
+        <v>8178</v>
       </c>
       <c r="D4" t="n">
-        <v>11564</v>
+        <v>7796</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1890</v>
+        <v>678</v>
       </c>
       <c r="C5" t="n">
-        <v>8012</v>
+        <v>10902</v>
       </c>
       <c r="D5" t="n">
-        <v>4182</v>
+        <v>3462</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>865</v>
+        <v>231</v>
       </c>
       <c r="C6" t="n">
-        <v>5456</v>
+        <v>8268</v>
       </c>
       <c r="D6" t="n">
-        <v>1205</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>149</v>
+        <v>62</v>
       </c>
       <c r="C7" t="n">
-        <v>3016</v>
+        <v>2911</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>1229</v>
+        <v>827</v>
       </c>
       <c r="D8" t="n">
-        <v>372</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3932</v>
+        <v>166</v>
       </c>
       <c r="C2" t="n">
-        <v>7028</v>
+        <v>2215</v>
       </c>
       <c r="D2" t="n">
-        <v>13997</v>
+        <v>6974</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2890</v>
+        <v>404</v>
       </c>
       <c r="C3" t="n">
-        <v>3043</v>
+        <v>5396</v>
       </c>
       <c r="D3" t="n">
-        <v>17687</v>
+        <v>9454</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3390</v>
+        <v>820</v>
       </c>
       <c r="C4" t="n">
-        <v>5807</v>
+        <v>7233</v>
       </c>
       <c r="D4" t="n">
-        <v>12367</v>
+        <v>7624</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2311</v>
+        <v>631</v>
       </c>
       <c r="C5" t="n">
-        <v>7551</v>
+        <v>8571</v>
       </c>
       <c r="D5" t="n">
-        <v>5117</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1124</v>
+        <v>228</v>
       </c>
       <c r="C6" t="n">
-        <v>6515</v>
+        <v>7742</v>
       </c>
       <c r="D6" t="n">
-        <v>1589</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>324</v>
+        <v>51</v>
       </c>
       <c r="C7" t="n">
-        <v>4030</v>
+        <v>3628</v>
       </c>
       <c r="D7" t="n">
-        <v>641</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1883</v>
+        <v>991</v>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>604</v>
+        <v>270</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>116</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2712</v>
+        <v>484</v>
       </c>
       <c r="C2" t="n">
-        <v>4821</v>
+        <v>16514</v>
       </c>
       <c r="D2" t="n">
-        <v>10204</v>
+        <v>9696</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2824</v>
+        <v>246</v>
       </c>
       <c r="C3" t="n">
-        <v>4168</v>
+        <v>3271</v>
       </c>
       <c r="D3" t="n">
-        <v>16451</v>
+        <v>8411</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2991</v>
+        <v>556</v>
       </c>
       <c r="C4" t="n">
-        <v>4739</v>
+        <v>6164</v>
       </c>
       <c r="D4" t="n">
-        <v>12773</v>
+        <v>7726</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2514</v>
+        <v>650</v>
       </c>
       <c r="C5" t="n">
-        <v>7064</v>
+        <v>7711</v>
       </c>
       <c r="D5" t="n">
-        <v>5776</v>
+        <v>4195</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1318</v>
+        <v>365</v>
       </c>
       <c r="C6" t="n">
-        <v>7099</v>
+        <v>8141</v>
       </c>
       <c r="D6" t="n">
-        <v>1921</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>4889</v>
+        <v>5561</v>
       </c>
       <c r="D7" t="n">
-        <v>711</v>
+        <v>650</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>2393</v>
+        <v>2189</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>684</v>
+        <v>576</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5041</v>
+        <v>487</v>
       </c>
       <c r="C2" t="n">
-        <v>5552</v>
+        <v>22397</v>
       </c>
       <c r="D2" t="n">
-        <v>12695</v>
+        <v>16886</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2344</v>
+        <v>284</v>
       </c>
       <c r="C3" t="n">
-        <v>3937</v>
+        <v>8175</v>
       </c>
       <c r="D3" t="n">
-        <v>14648</v>
+        <v>8020</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2549</v>
+        <v>372</v>
       </c>
       <c r="C4" t="n">
-        <v>4399</v>
+        <v>4647</v>
       </c>
       <c r="D4" t="n">
-        <v>12914</v>
+        <v>7602</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2443</v>
+        <v>561</v>
       </c>
       <c r="C5" t="n">
-        <v>5979</v>
+        <v>6763</v>
       </c>
       <c r="D5" t="n">
-        <v>6540</v>
+        <v>4569</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1596</v>
+        <v>440</v>
       </c>
       <c r="C6" t="n">
-        <v>7025</v>
+        <v>7867</v>
       </c>
       <c r="D6" t="n">
-        <v>2377</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>543</v>
+        <v>190</v>
       </c>
       <c r="C7" t="n">
-        <v>5757</v>
+        <v>6696</v>
       </c>
       <c r="D7" t="n">
-        <v>846</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>3248</v>
+        <v>3609</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>1243</v>
+        <v>1223</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>364</v>
+        <v>327</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6104</v>
+        <v>4658</v>
       </c>
       <c r="C2" t="n">
-        <v>10578</v>
+        <v>23560</v>
       </c>
       <c r="D2" t="n">
-        <v>5774</v>
+        <v>5216</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3642</v>
+        <v>575</v>
       </c>
       <c r="C2" t="n">
-        <v>3198</v>
+        <v>20948</v>
       </c>
       <c r="D2" t="n">
-        <v>9343</v>
+        <v>13704</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3225</v>
+        <v>296</v>
       </c>
       <c r="C3" t="n">
-        <v>4645</v>
+        <v>12379</v>
       </c>
       <c r="D3" t="n">
-        <v>15742</v>
+        <v>8570</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3558</v>
+        <v>292</v>
       </c>
       <c r="C4" t="n">
-        <v>6495</v>
+        <v>6074</v>
       </c>
       <c r="D4" t="n">
-        <v>13099</v>
+        <v>7358</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1519</v>
+        <v>456</v>
       </c>
       <c r="C5" t="n">
-        <v>9353</v>
+        <v>5683</v>
       </c>
       <c r="D5" t="n">
-        <v>5873</v>
+        <v>4866</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>501</v>
+        <v>448</v>
       </c>
       <c r="C6" t="n">
-        <v>7018</v>
+        <v>7352</v>
       </c>
       <c r="D6" t="n">
-        <v>1886</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>253</v>
       </c>
       <c r="C7" t="n">
-        <v>3183</v>
+        <v>7086</v>
       </c>
       <c r="D7" t="n">
-        <v>531</v>
+        <v>967</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="C8" t="n">
-        <v>1218</v>
+        <v>4787</v>
       </c>
       <c r="D8" t="n">
-        <v>293</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>356</v>
+        <v>2087</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>630</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7301</v>
+        <v>4786</v>
       </c>
       <c r="C2" t="n">
-        <v>4937</v>
+        <v>12639</v>
       </c>
       <c r="D2" t="n">
-        <v>12385</v>
+        <v>11330</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2593</v>
+        <v>1503</v>
       </c>
       <c r="C3" t="n">
-        <v>5331</v>
+        <v>9304</v>
       </c>
       <c r="D3" t="n">
-        <v>1609</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5233</v>
+        <v>3893</v>
       </c>
       <c r="C2" t="n">
-        <v>4412</v>
+        <v>8798</v>
       </c>
       <c r="D2" t="n">
-        <v>19180</v>
+        <v>13540</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4061</v>
+        <v>2656</v>
       </c>
       <c r="C3" t="n">
-        <v>4405</v>
+        <v>9686</v>
       </c>
       <c r="D3" t="n">
-        <v>3300</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1161</v>
+        <v>720</v>
       </c>
       <c r="C4" t="n">
-        <v>3167</v>
+        <v>5765</v>
       </c>
       <c r="D4" t="n">
-        <v>1505</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5647</v>
+        <v>2482</v>
       </c>
       <c r="C2" t="n">
-        <v>9428</v>
+        <v>7715</v>
       </c>
       <c r="D2" t="n">
-        <v>25419</v>
+        <v>18545</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3815</v>
+        <v>2697</v>
       </c>
       <c r="C3" t="n">
-        <v>3816</v>
+        <v>7919</v>
       </c>
       <c r="D3" t="n">
-        <v>5603</v>
+        <v>4546</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2219</v>
+        <v>1466</v>
       </c>
       <c r="C4" t="n">
-        <v>3802</v>
+        <v>7941</v>
       </c>
       <c r="D4" t="n">
-        <v>1803</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>526</v>
+        <v>348</v>
       </c>
       <c r="C5" t="n">
-        <v>1827</v>
+        <v>3351</v>
       </c>
       <c r="D5" t="n">
-        <v>1206</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>264</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6064</v>
+        <v>2240</v>
       </c>
       <c r="C2" t="n">
-        <v>11573</v>
+        <v>10059</v>
       </c>
       <c r="D2" t="n">
-        <v>26914</v>
+        <v>23002</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3878</v>
+        <v>2147</v>
       </c>
       <c r="C3" t="n">
-        <v>5835</v>
+        <v>6772</v>
       </c>
       <c r="D3" t="n">
-        <v>8220</v>
+        <v>6502</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2534</v>
+        <v>1777</v>
       </c>
       <c r="C4" t="n">
-        <v>3730</v>
+        <v>7763</v>
       </c>
       <c r="D4" t="n">
-        <v>2441</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1122</v>
+        <v>751</v>
       </c>
       <c r="C5" t="n">
-        <v>2812</v>
+        <v>5748</v>
       </c>
       <c r="D5" t="n">
-        <v>1260</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>293</v>
+        <v>203</v>
       </c>
       <c r="C6" t="n">
-        <v>1058</v>
+        <v>1861</v>
       </c>
       <c r="D6" t="n">
-        <v>942</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>296</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>306</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6334</v>
+        <v>1924</v>
       </c>
       <c r="C2" t="n">
-        <v>6378</v>
+        <v>10512</v>
       </c>
       <c r="D2" t="n">
-        <v>25500</v>
+        <v>30664</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3590</v>
+        <v>1812</v>
       </c>
       <c r="C3" t="n">
-        <v>7231</v>
+        <v>7336</v>
       </c>
       <c r="D3" t="n">
-        <v>9861</v>
+        <v>8430</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1990</v>
+        <v>1686</v>
       </c>
       <c r="C4" t="n">
-        <v>3956</v>
+        <v>7087</v>
       </c>
       <c r="D4" t="n">
-        <v>2986</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>944</v>
+        <v>1053</v>
       </c>
       <c r="C5" t="n">
-        <v>2397</v>
+        <v>6634</v>
       </c>
       <c r="D5" t="n">
-        <v>1145</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>331</v>
+        <v>403</v>
       </c>
       <c r="C6" t="n">
-        <v>1289</v>
+        <v>3707</v>
       </c>
       <c r="D6" t="n">
-        <v>758</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>446</v>
+        <v>1029</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6483</v>
+        <v>2188</v>
       </c>
       <c r="C2" t="n">
-        <v>4446</v>
+        <v>7868</v>
       </c>
       <c r="D2" t="n">
-        <v>27115</v>
+        <v>24355</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4103</v>
+        <v>1541</v>
       </c>
       <c r="C3" t="n">
-        <v>5782</v>
+        <v>7712</v>
       </c>
       <c r="D3" t="n">
-        <v>11762</v>
+        <v>10887</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2421</v>
+        <v>1494</v>
       </c>
       <c r="C4" t="n">
-        <v>5854</v>
+        <v>6988</v>
       </c>
       <c r="D4" t="n">
-        <v>4252</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1309</v>
+        <v>1177</v>
       </c>
       <c r="C5" t="n">
-        <v>3260</v>
+        <v>6704</v>
       </c>
       <c r="D5" t="n">
-        <v>1481</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="C6" t="n">
-        <v>1900</v>
+        <v>4927</v>
       </c>
       <c r="D6" t="n">
-        <v>821</v>
+        <v>912</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="C7" t="n">
-        <v>916</v>
+        <v>2209</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>632</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>340</v>
+        <v>607</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5075</v>
+        <v>2039</v>
       </c>
       <c r="C2" t="n">
-        <v>7966</v>
+        <v>5098</v>
       </c>
       <c r="D2" t="n">
-        <v>21921</v>
+        <v>19602</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4359</v>
+        <v>2296</v>
       </c>
       <c r="C3" t="n">
-        <v>4394</v>
+        <v>11215</v>
       </c>
       <c r="D3" t="n">
-        <v>13371</v>
+        <v>11377</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2771</v>
+        <v>1087</v>
       </c>
       <c r="C4" t="n">
-        <v>5692</v>
+        <v>10528</v>
       </c>
       <c r="D4" t="n">
-        <v>5564</v>
+        <v>3421</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1634</v>
+        <v>558</v>
       </c>
       <c r="C5" t="n">
-        <v>4555</v>
+        <v>4828</v>
       </c>
       <c r="D5" t="n">
-        <v>1927</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>847</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>2596</v>
+        <v>2164</v>
       </c>
       <c r="D6" t="n">
-        <v>929</v>
+        <v>619</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>342</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>1426</v>
+        <v>594</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>624</v>
+        <v>274</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>274</v>
+        <v>231</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
